--- a/education_forms/046_hunter_education_registration_form--education_forms.xlsx
+++ b/education_forms/046_hunter_education_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -528,14 +528,10 @@
           <t>First Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Your first name</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -558,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -585,7 +581,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -597,18 +593,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -620,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -638,46 +634,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_all_of_the_above</t>
+          <t>select_education_state</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select All of the Above</t>
+          <t>Select Education State</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_options</t>
+          <t>select_education_county</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select All of the Above Options</t>
+          <t>Select Education County</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -700,7 +696,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -723,7 +719,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -746,7 +742,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -769,7 +765,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -789,30 +785,38 @@
           <t>Date of Education</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_education_state</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Select Education State</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Any additional information you would like to include</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -822,46 +826,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_education_county</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Education County</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hunter_education_registration_certificate_number</t>
+          <t>select_reg_cert</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hunter Education Registration Certificate Number</t>
+          <t>Select Reg Cert</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -873,18 +877,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_reg_cert_state</t>
+          <t>select_reg_cert_county</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select Reg Cert State</t>
+          <t>Select Reg Cert County</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -896,204 +900,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_reg_cert_county</t>
+          <t>select_reg_cert_state</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Reg Cert County</t>
+          <t>Select Reg Cert State</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>hunter_edu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Any additional information you would like to include</t>
-        </is>
-      </c>
+          <t>Hunter Edu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submit_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submit_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submit_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submit_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submit_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,10 +949,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1138,7 +977,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_choices</t>
+          <t>select_education_state_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1155,7 +994,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_choices</t>
+          <t>select_education_state_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1172,7 +1011,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_choices</t>
+          <t>select_education_state_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1189,7 +1028,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_options_choices</t>
+          <t>select_education_county_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1206,7 +1045,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_options_choices</t>
+          <t>select_education_county_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1223,7 +1062,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_all_of_the_above_options_choices</t>
+          <t>select_education_county_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1240,7 +1079,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_education_state_choices</t>
+          <t>select_reg_cert_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1257,7 +1096,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_education_state_choices</t>
+          <t>select_reg_cert_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1274,7 +1113,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_education_state_choices</t>
+          <t>select_reg_cert_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1291,7 +1130,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_education_county_choices</t>
+          <t>select_reg_cert_county_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1308,7 +1147,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_education_county_choices</t>
+          <t>select_reg_cert_county_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1325,7 +1164,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_education_county_choices</t>
+          <t>select_reg_cert_county_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1385,57 +1224,6 @@
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_reg_cert_county_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>utah</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_reg_cert_county_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>arizona</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_reg_cert_county_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nevada</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Nevada</t>
         </is>
